--- a/hr/마인드_근태연차_관리대장.xlsx
+++ b/hr/마인드_근태연차_관리대장.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>상시 5명 이상이 되는 순간 연차유급휴가·가산수당·연차사용촉진이 모두 법적 의무가 됩니다. 취업규칙과 이 대장을 함께 점검하세요.</t>
+          <t>상시 5명 이상이 되는 순간 연차유급휴가·연차사용촉진·주 12시간 연장 한도가 법적 의무로 전환됩니다. 가산수당은 이미 취업규칙으로 지급하고 있습니다.</t>
         </is>
       </c>
     </row>
@@ -61275,14 +61275,14 @@
     <row r="2006">
       <c r="A2006" s="2" t="inlineStr">
         <is>
-          <t>· 「연장시간」은 1일 8시간 초과분입니다. 마인드는 5인 미만 사업장이므로 가산수당(50%) 지급의무는 없고, 실제 근로시간에 대한 통상임금만 지급합니다. (취업규칙 제21조제2항)</t>
+          <t>· 「연장시간」은 1일 8시간 초과분입니다. 이 시간에는 통상임금의 50%를 가산해 지급합니다. 휴일근로는 8시간 이내 50%, 8시간 초과분은 100%입니다. (취업규칙 제21조제2항)</t>
         </is>
       </c>
     </row>
     <row r="2007">
       <c r="A2007" s="2" t="inlineStr">
         <is>
-          <t>· 5명 이상이 되면 이 열의 시간에 통상임금의 50%를 가산해야 하고, 주 12시간 연장 한도도 적용됩니다.</t>
+          <t>· 5인 미만 사업장에는 가산수당 지급의무가 법으로 강제되지 않지만, 마인드는 근로계약과 통일하기 위해 취업규칙으로 정해 지급합니다. 5명 이상이 되면 여기에 주 12시간 연장 한도가 더해집니다.</t>
         </is>
       </c>
     </row>

--- a/hr/마인드_근태연차_관리대장.xlsx
+++ b/hr/마인드_근태연차_관리대장.xlsx
@@ -993,48 +993,48 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>M001</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>홍길동</t>
+          <t>강성아</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
-        <v>45718</v>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C5" s="19" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>디자이너</t>
+          <t>UI·UX 디자이너</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>정규사원</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>재직</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="14" t="n">
-        <v>42000000</v>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="20" t="n">
+        <v>32000000</v>
       </c>
       <c r="I5" s="15">
         <f>IF(H5="","",ROUND(H5/12,0))</f>
         <v/>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>← 예시 행입니다. 실제 입력 전에 지우세요.</t>
+          <t>수습 2026-01-12 ~ 2026-04-11 종료</t>
         </is>
       </c>
     </row>
@@ -2620,39 +2620,17 @@
         <f>IF(B5="","",COUNTA($B$5:$B5))</f>
         <v/>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
+      <c r="B5" s="12" t="n"/>
       <c r="C5" s="25">
         <f>IFERROR(IF(B5="","",INDEX(직원명부!$B$5:$B$24,MATCH(B5,직원명부!$A$5:$A$24,0))),"사번 확인")</f>
         <v/>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>46146</v>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>연차</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>개인 사유</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>대표</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>46141</v>
-      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="30">
@@ -11253,31 +11231,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>46148</v>
-      </c>
+      <c r="A5" s="13" t="n"/>
       <c r="B5" s="25">
         <f>IF(A5="","",CHOOSE(WEEKDAY(A5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="25">
         <f>IFERROR(IF(C5="","",INDEX(직원명부!$B$5:$B$24,MATCH(C5,직원명부!$A$5:$A$24,0))),"사번 확인")</f>
         <v/>
       </c>
-      <c r="E5" s="32" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>0.7708333333333334</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="31" t="n"/>
       <c r="H5" s="33">
         <f>IF(OR(E5="",F5=""),"",ROUND(MOD(F5-E5,1)*24-N(G5),2))</f>
         <v/>
@@ -11286,16 +11252,8 @@
         <f>IF(H5="","",ROUND(MAX(0,H5-8),2))</f>
         <v/>
       </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>마감 대응</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="19" t="n"/>
